--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-22T11:57:51+00:00</t>
+    <t>2026-02-25T07:03:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T10:29:33+00:00</t>
+    <t>2026-03-01T15:46:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T15:46:45+00:00</t>
+    <t>2026-03-02T16:20:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2738,7 +2738,7 @@
     <t>AtPrenudgeObservationWHOQOLBrefScore</t>
   </si>
   <si>
-    <t xml:space="preserve"> AT PreNUDGE Observation WHOQOL-BREF Score</t>
+    <t>AT PreNUDGE Observation WHOQOL-BREF Score</t>
   </si>
   <si>
     <t>Observation profile for recording WHOQOL-BREF domain scores. The overall score is represented in Observation.value, individual domain scores are recorded as components.</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T16:20:44+00:00</t>
+    <t>2026-03-02T17:40:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T17:40:54+00:00</t>
+    <t>2026-03-03T16:09:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T16:09:57+00:00</t>
+    <t>2026-03-03T18:16:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T18:16:34+00:00</t>
+    <t>2026-03-03T20:10:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T11:22:25+00:00</t>
+    <t>2026-03-27T21:20:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2412,7 +2412,7 @@
     <t>QuestionnaireResponse.identifier</t>
   </si>
   <si>
-    <t>Unique id for this set of answers, at least one is assigned by the data provider</t>
+    <t>Mandatory date the answers were gathered</t>
   </si>
   <si>
     <t>A business identifier assigned to a particular completed (or partially completed) questionnaire.</t>
@@ -46059,7 +46059,7 @@
       </c>
       <c r="F391" s="2"/>
       <c r="G391" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H391" t="s" s="2">
         <v>85</v>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:39:37+00:00</t>
+    <t>2026-03-29T11:44:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-29T11:44:39+00:00</t>
+    <t>2026-04-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1294,8 +1294,8 @@
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
     &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="1556-0"/&gt;
-    &lt;display value="Fasting glucose [Mass/volume] in Capillary blood"/&gt;
+    &lt;code value="41653-7"/&gt;
+    &lt;display value="Glucose [Mass/volume] in Capillary blood by Glucometer"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -4889,7 +4889,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="57.69921875" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="63.81640625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="32.7734375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T14:50:23+00:00</t>
+    <t>2026-05-18T08:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18T08:38:27+00:00</t>
+    <t>2026-05-18T10:23:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:49:28+00:00</t>
+    <t>2026-06-03T09:07:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T09:07:40+00:00</t>
+    <t>2026-06-03T10:15:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T06:28:21+00:00</t>
+    <t>2026-06-18T08:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
